--- a/exports/INDUSTOWER_full_report.xlsx
+++ b/exports/INDUSTOWER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.19</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>253.6</v>
+        <v>249.75</v>
       </c>
       <c r="I2" t="n">
         <v>251.02426999145</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>1.02</v>
+        <v>-0.52</v>
       </c>
       <c r="L2" t="n">
         <v>2.57</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44650.38541666666</v>
+        <v>44650.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>206.65</v>
+        <v>212.3</v>
       </c>
       <c r="I3" t="n">
         <v>211.1243719637483</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>67.83333333333333</v>
+        <v>68</v>
       </c>
       <c r="K3" t="n">
-        <v>17.26</v>
+        <v>14.99</v>
       </c>
       <c r="L3" t="n">
         <v>3.78</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44677.55208333334</v>
+        <v>44678.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>205.05</v>
+        <v>199.05</v>
       </c>
       <c r="I4" t="n">
         <v>200.5845542141485</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.41</v>
+        <v>-6.24</v>
       </c>
       <c r="L4" t="n">
-        <v>4.55</v>
+        <v>6.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.66</v>
+        <v>1.29</v>
       </c>
       <c r="N4" t="n">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="O4" t="n">
         <v>2.36</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.38</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44707.38541666666</v>
+        <v>44707.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>194.8</v>
+        <v>195.7</v>
       </c>
       <c r="I5" t="n">
         <v>195.6079956129047</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="L5" t="n">
         <v>4.17</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.89</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44740.55208333334</v>
+        <v>44741.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>200.15</v>
+        <v>195.2</v>
       </c>
       <c r="I6" t="n">
         <v>195.7838266463623</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K6" t="n">
-        <v>2.27</v>
+        <v>-0.26</v>
       </c>
       <c r="L6" t="n">
         <v>3.93</v>
@@ -783,7 +854,7 @@
         <v>1.68</v>
       </c>
       <c r="N6" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.61</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44753.55208333334</v>
+        <v>44754.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>205.85</v>
+        <v>213.95</v>
       </c>
       <c r="I7" t="n">
         <v>209.9632499332305</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.46</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>7.63</v>
+        <v>10.84</v>
       </c>
       <c r="M7" t="n">
         <v>1.64</v>
       </c>
       <c r="N7" t="n">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="O7" t="n">
         <v>-2.6</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.64</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44775.55208333334</v>
+        <v>44776.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>211.45</v>
+        <v>196.05</v>
       </c>
       <c r="I8" t="n">
         <v>208.8545582604879</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.17</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>4.07</v>
+        <v>9.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>3.78</v>
+        <v>5.89</v>
       </c>
       <c r="O8" t="n">
         <v>3.47</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.83</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44834.38541666666</v>
+        <v>44834.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>187</v>
+        <v>190.35</v>
       </c>
       <c r="I9" t="n">
         <v>188.9544812642945</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>4.62</v>
+        <v>2.91</v>
       </c>
       <c r="L9" t="n">
         <v>4.85</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.37</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44846.55208333334</v>
+        <v>44847.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>184.4</v>
+        <v>181.35</v>
       </c>
       <c r="I10" t="n">
         <v>182.0042594635707</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.13</v>
+        <v>-4.73</v>
       </c>
       <c r="L10" t="n">
-        <v>4.12</v>
+        <v>5.02</v>
       </c>
       <c r="M10" t="n">
         <v>1.19</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.63</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44879.38541666666</v>
+        <v>44879.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>186.05</v>
+        <v>186.75</v>
       </c>
       <c r="I11" t="n">
         <v>186.4726887183223</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.59</v>
+        <v>-2.98</v>
       </c>
       <c r="L11" t="n">
         <v>4.47</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.54</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>189.1</v>
+        <v>187.95</v>
       </c>
       <c r="I12" t="n">
         <v>188.7664208320521</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>1.26</v>
+        <v>0.64</v>
       </c>
       <c r="L12" t="n">
         <v>1.15</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>4.27</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>139.15</v>
+        <v>156.45</v>
       </c>
       <c r="I13" t="n">
         <v>148.4460838004821</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>25.96</v>
+        <v>16.76</v>
       </c>
       <c r="L13" t="n">
         <v>3.78</v>
       </c>
       <c r="M13" t="n">
-        <v>4.89</v>
+        <v>7.33</v>
       </c>
       <c r="N13" t="n">
-        <v>7.53</v>
+        <v>12.9</v>
       </c>
       <c r="O13" t="n">
         <v>-0.77</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>15.18</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44994.38541666666</v>
+        <v>44994.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>153</v>
+        <v>151.35</v>
       </c>
       <c r="I14" t="n">
         <v>151.7436195454849</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.21</v>
+        <v>-3.26</v>
       </c>
       <c r="L14" t="n">
         <v>4.54</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.93</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45041.55208333334</v>
+        <v>45042.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>133.2</v>
+        <v>137.65</v>
       </c>
       <c r="I15" t="n">
         <v>137.0501371339299</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>11.99</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -1296,7 +1475,7 @@
         <v>0.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="O15" t="n">
         <v>-2.17</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.73</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45064.55208333334</v>
+        <v>45065.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>142.05</v>
+        <v>140.1</v>
       </c>
       <c r="I16" t="n">
         <v>140.8925994955994</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="L16" t="n">
         <v>3.38</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>7.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45071.55208333334</v>
+        <v>45072.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>142.65</v>
+        <v>150.95</v>
       </c>
       <c r="I17" t="n">
         <v>145.1957438067769</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.82</v>
+        <v>-7.74</v>
       </c>
       <c r="L17" t="n">
-        <v>2.96</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>0.53</v>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>5.85</v>
       </c>
       <c r="O17" t="n">
         <v>-1.72</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>163.6</v>
+        <v>156.1</v>
       </c>
       <c r="I18" t="n">
         <v>162.4657216179075</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>80.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K18" t="n">
-        <v>8.380000000000001</v>
+        <v>3.41</v>
       </c>
       <c r="L18" t="n">
         <v>6.13</v>
@@ -1467,7 +1682,7 @@
         <v>2.38</v>
       </c>
       <c r="N18" t="n">
-        <v>2.77</v>
+        <v>5.32</v>
       </c>
       <c r="O18" t="n">
         <v>5.85</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45163.38541666666</v>
+        <v>45163.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>160.15</v>
+        <v>161.55</v>
       </c>
       <c r="I19" t="n">
         <v>161.1200992151134</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.59</v>
+        <v>-3.49</v>
       </c>
       <c r="L19" t="n">
         <v>5.38</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.81</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>175.65</v>
+        <v>171.85</v>
       </c>
       <c r="I20" t="n">
         <v>172.3417476979737</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>8.73</v>
+        <v>6.38</v>
       </c>
       <c r="L20" t="n">
         <v>1.21</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45210.38541666666</v>
+        <v>45210.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>183.3</v>
+        <v>185.35</v>
       </c>
       <c r="I21" t="n">
         <v>183.8462348138331</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.66</v>
+        <v>-7.86</v>
       </c>
       <c r="L21" t="n">
         <v>10.56</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.28</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>177.4</v>
+        <v>172.55</v>
       </c>
       <c r="I22" t="n">
         <v>175.7075430243017</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.29</v>
+        <v>-6.91</v>
       </c>
       <c r="L22" t="n">
-        <v>4.83</v>
+        <v>7.01</v>
       </c>
       <c r="M22" t="n">
         <v>0.39</v>
       </c>
       <c r="N22" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
         <v>2.97</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.51</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45230.55208333334</v>
+        <v>45231.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>166.65</v>
+        <v>175.15</v>
       </c>
       <c r="I23" t="n">
         <v>175.0928464147875</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
-        <v>3.42</v>
+        <v>-1.51</v>
       </c>
       <c r="L23" t="n">
         <v>3.33</v>
@@ -1752,7 +2027,7 @@
         <v>1.75</v>
       </c>
       <c r="N23" t="n">
-        <v>1.77</v>
+        <v>4.44</v>
       </c>
       <c r="O23" t="n">
         <v>-3.35</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.33</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>182.9</v>
+        <v>173.4</v>
       </c>
       <c r="I24" t="n">
         <v>179.9071652031529</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>4.42</v>
+        <v>-1</v>
       </c>
       <c r="L24" t="n">
         <v>5.11</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>11.3</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45288.55208333334</v>
+        <v>45289.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>179.3</v>
+        <v>190.8</v>
       </c>
       <c r="I25" t="n">
         <v>190.3674027536657</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.4</v>
+        <v>-10.03</v>
       </c>
       <c r="L25" t="n">
-        <v>5.51</v>
+        <v>10.61</v>
       </c>
       <c r="M25" t="n">
         <v>0.64</v>
       </c>
       <c r="N25" t="n">
-        <v>3.72</v>
+        <v>6.44</v>
       </c>
       <c r="O25" t="n">
         <v>-8.4</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.59</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45335.38541666666</v>
+        <v>45335.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>205.4</v>
+        <v>201.85</v>
       </c>
       <c r="I26" t="n">
         <v>204.0838610333729</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>7.65</v>
+        <v>5.79</v>
       </c>
       <c r="L26" t="n">
         <v>6.66</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.89</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45344.55208333334</v>
+        <v>45345.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>217.8</v>
+        <v>233.75</v>
       </c>
       <c r="I27" t="n">
         <v>223.8318774443482</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.9</v>
+        <v>-15.8</v>
       </c>
       <c r="L27" t="n">
-        <v>8.869999999999999</v>
+        <v>16.25</v>
       </c>
       <c r="M27" t="n">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>6.45</v>
       </c>
       <c r="O27" t="n">
         <v>-2.13</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>237.85</v>
+        <v>231.4</v>
       </c>
       <c r="I28" t="n">
         <v>233.2657477041022</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>1.75</v>
+        <v>-1.01</v>
       </c>
       <c r="L28" t="n">
         <v>4.73</v>
@@ -2037,7 +2372,7 @@
         <v>0.48</v>
       </c>
       <c r="N28" t="n">
-        <v>3.04</v>
+        <v>5.55</v>
       </c>
       <c r="O28" t="n">
         <v>6.45</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.07</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>240.85</v>
+        <v>250.9</v>
       </c>
       <c r="I29" t="n">
         <v>250.0442401569014</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.08</v>
+        <v>-8.43</v>
       </c>
       <c r="L29" t="n">
-        <v>6.11</v>
+        <v>8.56</v>
       </c>
       <c r="M29" t="n">
         <v>1.88</v>
       </c>
       <c r="N29" t="n">
-        <v>5.85</v>
+        <v>10.11</v>
       </c>
       <c r="O29" t="n">
         <v>-5.55</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.75</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>325.55</v>
+        <v>318.5</v>
       </c>
       <c r="I30" t="n">
         <v>318.9063036701413</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K30" t="n">
-        <v>29.75</v>
+        <v>26.94</v>
       </c>
       <c r="L30" t="n">
         <v>3.89</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>9.17</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>332.4</v>
+        <v>342.7</v>
       </c>
       <c r="I31" t="n">
         <v>338.6995275169493</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.36</v>
+        <v>-7.6</v>
       </c>
       <c r="L31" t="n">
-        <v>7.85</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>0.92</v>
+        <v>4.53</v>
       </c>
       <c r="N31" t="n">
-        <v>3.43</v>
+        <v>5.67</v>
       </c>
       <c r="O31" t="n">
         <v>-2.67</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>351.25</v>
+        <v>302</v>
       </c>
       <c r="I32" t="n">
         <v>325.2917645365034</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>2.49</v>
+        <v>-11.88</v>
       </c>
       <c r="L32" t="n">
-        <v>3.91</v>
+        <v>17.89</v>
       </c>
       <c r="M32" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>15.47</v>
       </c>
       <c r="O32" t="n">
         <v>5.67</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>18.68</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45469.55208333334</v>
+        <v>45470.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>343.8</v>
+        <v>349.3</v>
       </c>
       <c r="I33" t="n">
         <v>349.0786707254322</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>-13.84</v>
+        <v>-15.66</v>
       </c>
       <c r="L33" t="n">
-        <v>15.84</v>
+        <v>16.71</v>
       </c>
       <c r="M33" t="n">
         <v>3.64</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.72</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>405.75</v>
+        <v>398.8</v>
       </c>
       <c r="I34" t="n">
         <v>401.78096729625</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K34" t="n">
-        <v>16.16</v>
+        <v>14.17</v>
       </c>
       <c r="L34" t="n">
         <v>3.08</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.96</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45524.38541666666</v>
+        <v>45524.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>409.25</v>
+        <v>414.1</v>
       </c>
       <c r="I35" t="n">
         <v>412.1739055951348</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.62</v>
+        <v>-3.84</v>
       </c>
       <c r="L35" t="n">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
         <v>1.31</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>5.49</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>425.3</v>
+        <v>417.25</v>
       </c>
       <c r="I36" t="n">
         <v>418.1846821391355</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>2.7</v>
+        <v>0.76</v>
       </c>
       <c r="L36" t="n">
         <v>1.44</v>
       </c>
       <c r="M36" t="n">
-        <v>0.39</v>
+        <v>1.45</v>
       </c>
       <c r="N36" t="n">
         <v>4.06</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.73</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45621.38541666666</v>
+        <v>45621.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>322.65</v>
+        <v>327</v>
       </c>
       <c r="I37" t="n">
         <v>323.9244001382576</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>82</v>
+        <v>82.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>22.67</v>
+        <v>21.63</v>
       </c>
       <c r="L37" t="n">
         <v>2.68</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.73</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45638.38541666666</v>
+        <v>45638.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>333.65</v>
+        <v>331</v>
       </c>
       <c r="I38" t="n">
         <v>333.3615307616629</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>2.03</v>
+        <v>1.22</v>
       </c>
       <c r="L38" t="n">
         <v>1.65</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>6.22</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>328.55</v>
+        <v>341.25</v>
       </c>
       <c r="I39" t="n">
         <v>330.1426768525259</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>0.74</v>
+        <v>-3.1</v>
       </c>
       <c r="L39" t="n">
-        <v>4.61</v>
+        <v>5.17</v>
       </c>
       <c r="M39" t="n">
         <v>2.05</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.32</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>340.15</v>
+        <v>335.9</v>
       </c>
       <c r="I40" t="n">
         <v>336.9124798391247</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.32</v>
+        <v>-1.57</v>
       </c>
       <c r="L40" t="n">
         <v>4.22</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.81</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45737.38541666666</v>
+        <v>45737.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>332.7</v>
+        <v>336.8</v>
       </c>
       <c r="I41" t="n">
         <v>333.7523313318603</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>52.83333333333334</v>
+        <v>53</v>
       </c>
       <c r="K41" t="n">
-        <v>0.95</v>
+        <v>-0.27</v>
       </c>
       <c r="L41" t="n">
         <v>5.97</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.15</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>391.25</v>
+        <v>368.85</v>
       </c>
       <c r="I42" t="n">
         <v>372.2570776619895</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>40</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>16.17</v>
+        <v>9.52</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
@@ -2835,7 +3338,7 @@
         <v>5.73</v>
       </c>
       <c r="N42" t="n">
-        <v>3.14</v>
+        <v>6.75</v>
       </c>
       <c r="O42" t="n">
         <v>2.76</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>374.4</v>
+        <v>383.95</v>
       </c>
       <c r="I43" t="n">
         <v>381.1243900668794</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.5</v>
+        <v>-4.09</v>
       </c>
       <c r="L43" t="n">
         <v>6.44</v>
@@ -2892,7 +3407,7 @@
         <v>1.42</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
         <v>-6.75</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.2</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45845.55208333334</v>
+        <v>45846.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>393.2</v>
+        <v>391.7</v>
       </c>
       <c r="I44" t="n">
         <v>392.8739045314139</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="L44" t="n">
         <v>2.24</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.93</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>329.05</v>
+        <v>338.3</v>
       </c>
       <c r="I45" t="n">
         <v>337.4627757115417</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>15.99</v>
+        <v>13.63</v>
       </c>
       <c r="L45" t="n">
         <v>1.21</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.9</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>325.9</v>
+        <v>323.95</v>
       </c>
       <c r="I46" t="n">
         <v>324.2336175976259</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.67</v>
+        <v>-4.24</v>
       </c>
       <c r="L46" t="n">
-        <v>3.8</v>
+        <v>4.67</v>
       </c>
       <c r="M46" t="n">
         <v>2.61</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.99</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>324.8</v>
+        <v>332.15</v>
       </c>
       <c r="I47" t="n">
         <v>328.5826826652633</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.26</v>
+        <v>-2.53</v>
       </c>
       <c r="L47" t="n">
         <v>3.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.75</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>342.95</v>
+        <v>333.95</v>
       </c>
       <c r="I48" t="n">
         <v>334.4878682180001</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>3.25</v>
+        <v>0.54</v>
       </c>
       <c r="L48" t="n">
         <v>2.83</v>
@@ -3177,7 +3752,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="O48" t="n">
         <v>2.37</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>6.71</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45950.55208333334</v>
+        <v>45951.57291666666</v>
       </c>
       <c r="H49" t="n">
-        <v>342.35</v>
+        <v>346.85</v>
       </c>
       <c r="I49" t="n">
         <v>343.8789966974589</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25.1875</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.52</v>
+        <v>-3.86</v>
       </c>
       <c r="L49" t="n">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="M49" t="n">
         <v>0.71</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.39</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45961.38541666666</v>
+        <v>45961.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>355.6</v>
+        <v>350.85</v>
       </c>
       <c r="I50" t="n">
         <v>350.931399123612</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>9.8125</v>
+        <v>9.979166666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>2.52</v>
+        <v>1.15</v>
       </c>
       <c r="L50" t="n">
         <v>1.74</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>6.42</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>368.85</v>
+        <v>376.65</v>
       </c>
       <c r="I51" t="n">
         <v>373.3900958814983</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.13</v>
+        <v>-7.35</v>
       </c>
       <c r="L51" t="n">
-        <v>5.63</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>0.54</v>
+        <v>2.43</v>
       </c>
       <c r="N51" t="n">
         <v>5.13</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.22</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46042.38541666666</v>
+        <v>46042.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>403.85</v>
+        <v>399.05</v>
       </c>
       <c r="I52" t="n">
         <v>402.6952073164867</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>77</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>7.22</v>
+        <v>5.95</v>
       </c>
       <c r="L52" t="n">
         <v>1.08</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.6</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>409.75</v>
+        <v>424.9</v>
       </c>
       <c r="I53" t="n">
         <v>420.8692287212862</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.68</v>
+        <v>-6.48</v>
       </c>
       <c r="L53" t="n">
-        <v>3.51</v>
+        <v>6.52</v>
       </c>
       <c r="M53" t="n">
         <v>0.98</v>
       </c>
       <c r="N53" t="n">
-        <v>2.37</v>
+        <v>3.82</v>
       </c>
       <c r="O53" t="n">
         <v>-3.12</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>7.64</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>437.25</v>
+        <v>429.1</v>
       </c>
       <c r="I54" t="n">
         <v>435.3518219666725</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K54" t="n">
-        <v>2.91</v>
+        <v>0.99</v>
       </c>
       <c r="L54" t="n">
         <v>5.19</v>
       </c>
       <c r="M54" t="n">
-        <v>0.71</v>
+        <v>3.21</v>
       </c>
       <c r="N54" t="n">
         <v>4.77</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.94</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>407.95</v>
+        <v>416.15</v>
       </c>
       <c r="I55" t="n">
         <v>408.4575014845152</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K55" t="n">
-        <v>4.93</v>
+        <v>3.02</v>
       </c>
       <c r="L55" t="n">
         <v>3.16</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>404.45</v>
+        <v>400.3</v>
       </c>
       <c r="I56" t="n">
         <v>404.3690660186039</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.81</v>
+        <v>-3.81</v>
       </c>
       <c r="L56" t="n">
-        <v>3.21</v>
+        <v>5.38</v>
       </c>
       <c r="M56" t="n">
         <v>0.82</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.45</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46212.55208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>384.4</v>
+        <v>389.9</v>
       </c>
       <c r="I57" t="n">
         <v>387.2883169434451</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K57" t="n">
-        <v>3.97</v>
+        <v>2.6</v>
       </c>
       <c r="L57" t="n">
         <v>2.69</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>7.04</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46230.38541666666</v>
+        <v>46230.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>378</v>
+        <v>371.5</v>
       </c>
       <c r="I58" t="n">
         <v>376.1903442046398</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.05</v>
+        <v>-4.72</v>
       </c>
       <c r="L58" t="n">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="M58" t="n">
         <v>1.64</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.96</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46275.55208333334</v>
+        <v>46276.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>372</v>
+        <v>388.5</v>
       </c>
       <c r="I59" t="n">
         <v>385.8265756208788</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>45</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.13</v>
+        <v>-4.58</v>
       </c>
       <c r="L59" t="n">
-        <v>4.82</v>
+        <v>5.21</v>
       </c>
       <c r="M59" t="n">
         <v>1.21</v>
       </c>
       <c r="N59" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="O59" t="n">
         <v>-2.39</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.7</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>374.25</v>
+        <v>369.25</v>
       </c>
       <c r="I60" t="n">
         <v>370.7225042581218</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.67</v>
+        <v>-4.95</v>
       </c>
       <c r="L60" t="n">
-        <v>4.25</v>
+        <v>5.69</v>
       </c>
       <c r="M60" t="n">
         <v>0.92</v>
       </c>
       <c r="N60" t="n">
-        <v>2.18</v>
+        <v>3.99</v>
       </c>
       <c r="O60" t="n">
         <v>4.29</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>4.72</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>380.2</v>
+        <v>389.85</v>
       </c>
       <c r="I61" t="n">
         <v>381.2345316395595</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.97</v>
+        <v>-5.58</v>
       </c>
       <c r="L61" t="n">
-        <v>4.18</v>
+        <v>6.24</v>
       </c>
       <c r="M61" t="n">
         <v>1.5</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,12 @@
       <c r="Q62" t="n">
         <v>30</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6080,7 +6829,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.9</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="6">
@@ -6090,7 +6839,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="7">
@@ -6100,7 +6849,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="8">
@@ -6110,7 +6859,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6120,7 +6869,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="10">
@@ -6130,7 +6879,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="11">
@@ -6140,7 +6889,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -6150,7 +6899,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6160,7 +6909,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="14">
@@ -6170,7 +6919,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.38</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="15">
@@ -6180,7 +6929,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.29</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="16">
@@ -6190,7 +6939,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.47</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="17">
@@ -6200,7 +6949,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.75</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="18">
@@ -6210,7 +6959,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6220,7 +6969,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.35</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="20">
@@ -6230,7 +6979,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.1</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="21">
@@ -6240,7 +6989,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.84</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="22">
@@ -6250,7 +6999,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -6260,7 +7009,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6270,7 +7019,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
@@ -6280,7 +7029,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.73</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="26">
@@ -6290,7 +7039,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.67</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +7049,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.4</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="28">
@@ -6310,7 +7059,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
